--- a/source/syzdirect/Runner/dataset_hunt.xlsx
+++ b/source/syzdirect/Runner/dataset_hunt.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,22 +449,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TEQL qdisc UAF in teql_destroy</t>
+          <t>TC tcindex race in tcindex_alloc_perfect_hash</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ac0b8b327a56</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>socket$nl_route,sendmsg$nl_route_newqdisc,sendmsg$nl_route_delqdisc</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>/home/ai/syzdirect-runtime/cve/new_hunt_teql_uaf/kernel-build/.config</t>
+          <t>304040fb4909</t>
         </is>
       </c>
     </row>
@@ -474,22 +464,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CEC adapter race in __cec_s_phys_addr</t>
+          <t>TC qdisc create bug in qdisc_create</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ac0b8b327a56</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>openat$cec,ioctl$CEC_ADAP_S_PHYS_ADDR,ioctl$CEC_TRANSMIT</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>/home/ai/syzdirect-runtime/cve/new_hunt_teql_uaf/kernel-build/.config</t>
+          <t>304040fb4909</t>
         </is>
       </c>
     </row>
@@ -499,22 +479,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HFSC qdisc class change race in hfsc_change_class</t>
+          <t>TC fifo limit bug in fifo_set_limit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ac0b8b327a56</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>socket$nl_route,sendmsg$nl_route_newqdisc,sendmsg$nl_route_newtclass</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>/home/ai/syzdirect-runtime/cve/new_hunt_teql_uaf/kernel-build/.config</t>
+          <t>304040fb4909</t>
         </is>
       </c>
     </row>
@@ -524,72 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Packet socket fanout race in fanout_add</t>
+          <t>TCP congestion control bug in tcp_cleanup_congestion_control</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ac0b8b327a56</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>socket$packet,setsockopt$PACKET_FANOUT,bind$packet</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>/home/ai/syzdirect-runtime/cve/new_hunt_teql_uaf/kernel-build/.config</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>vsock virtio transport close race</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ac0b8b327a56</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>socket$vsock_stream,connect$vsock,shutdown,close</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>/home/ai/syzdirect-runtime/cve/new_hunt_teql_uaf/kernel-build/.config</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BPF verifier edge case in do_check</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ac0b8b327a56</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>bpf$BPF_PROG_LOAD,bpf$BPF_MAP_CREATE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>/home/ai/syzdirect-runtime/cve/new_hunt_teql_uaf/kernel-build/.config</t>
+          <t>304040fb4909</t>
         </is>
       </c>
     </row>
